--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,6 +1233,941 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124939853</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596692</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6923986</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hackring av tretåig hackspett av tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124941916</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596692</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6923986</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124937714</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596676</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6923916</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124937225</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596705</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6923956</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124933804</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596645</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6924182</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124937848</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596681</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6923921</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124936750</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596731</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6923972</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124938227</v>
+      </c>
+      <c r="B14" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>596692</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6923986</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1819,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937848</v>
+        <v>124936750</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,16 +1835,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596681</v>
+        <v>596731</v>
       </c>
       <c r="R12" t="n">
-        <v>6923921</v>
+        <v>6923972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,22 +1929,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124936750</v>
+        <v>124937848</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,16 +1957,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,7 +1977,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1981,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596731</v>
+        <v>596681</v>
       </c>
       <c r="R13" t="n">
-        <v>6923972</v>
+        <v>6923921</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,12 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,12 +2046,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939853</v>
+        <v>124941916</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,16 +1251,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1268,10 +1268,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hackring av tretåig hackspett av tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124941916</v>
+        <v>124936750</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,16 +1372,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1390,26 +1389,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596692</v>
+        <v>596731</v>
       </c>
       <c r="R8" t="n">
-        <v>6923986</v>
+        <v>6923972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937714</v>
+        <v>124933804</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1494,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596676</v>
+        <v>596645</v>
       </c>
       <c r="R9" t="n">
-        <v>6923916</v>
+        <v>6924182</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937225</v>
+        <v>124936892</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,34 +1611,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596705</v>
+        <v>596692</v>
       </c>
       <c r="R10" t="n">
-        <v>6923956</v>
+        <v>6923986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1688,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,22 +1708,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933804</v>
+        <v>124937225</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,39 +1736,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596645</v>
+        <v>596705</v>
       </c>
       <c r="R11" t="n">
-        <v>6924182</v>
+        <v>6923956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1805,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,22 +1820,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124936750</v>
+        <v>124938227</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,39 +1848,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596731</v>
+        <v>596692</v>
       </c>
       <c r="R12" t="n">
-        <v>6923972</v>
+        <v>6923986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,12 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,22 +1932,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124937848</v>
+        <v>124937714</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,39 +1960,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596681</v>
+        <v>596676</v>
       </c>
       <c r="R13" t="n">
-        <v>6923921</v>
+        <v>6923916</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124938227</v>
+        <v>124937848</v>
       </c>
       <c r="B14" t="n">
-        <v>82597</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,34 +2072,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596692</v>
+        <v>596681</v>
       </c>
       <c r="R14" t="n">
-        <v>6923986</v>
+        <v>6923921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,12 +2161,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941916</v>
+        <v>124936750</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,16 +1251,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1268,26 +1268,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596692</v>
+        <v>596731</v>
       </c>
       <c r="R7" t="n">
-        <v>6923986</v>
+        <v>6923972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1325,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,19 +1345,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124936750</v>
+        <v>124939853</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1397,14 +1398,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596731</v>
+        <v>596692</v>
       </c>
       <c r="R8" t="n">
-        <v>6923972</v>
+        <v>6923986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre hackring av tretåig hackspett av tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124933804</v>
+        <v>124938227</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>82597</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,39 +1495,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596645</v>
+        <v>596692</v>
       </c>
       <c r="R9" t="n">
-        <v>6924182</v>
+        <v>6923986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1579,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124936892</v>
+        <v>124933804</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,16 +1607,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1629,24 +1625,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596692</v>
+        <v>596645</v>
       </c>
       <c r="R10" t="n">
-        <v>6923986</v>
+        <v>6924182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,12 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,22 +1696,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937225</v>
+        <v>124937848</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,34 +1724,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596705</v>
+        <v>596681</v>
       </c>
       <c r="R11" t="n">
-        <v>6923956</v>
+        <v>6923921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,22 +1813,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124938227</v>
+        <v>124937714</v>
       </c>
       <c r="B12" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,34 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596692</v>
+        <v>596676</v>
       </c>
       <c r="R12" t="n">
-        <v>6923986</v>
+        <v>6923916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,19 +1925,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124937714</v>
+        <v>124937225</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1980,14 +1973,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596676</v>
+        <v>596705</v>
       </c>
       <c r="R13" t="n">
-        <v>6923916</v>
+        <v>6923956</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,19 +2037,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124937848</v>
+        <v>124941916</v>
       </c>
       <c r="B14" t="n">
         <v>57529</v>
@@ -2089,7 +2082,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2097,14 +2094,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596681</v>
+        <v>596692</v>
       </c>
       <c r="R14" t="n">
-        <v>6923921</v>
+        <v>6923986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,12 +2158,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124936750</v>
+        <v>124936892</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1269,21 +1269,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596731</v>
+        <v>596692</v>
       </c>
       <c r="R7" t="n">
-        <v>6923972</v>
+        <v>6923986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1328,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,19 +1348,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939853</v>
+        <v>124936750</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1398,14 +1401,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596692</v>
+        <v>596731</v>
       </c>
       <c r="R8" t="n">
-        <v>6923986</v>
+        <v>6923972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre hackring av tretåig hackspett av tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1470,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1591,7 +1594,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933804</v>
+        <v>124941916</v>
       </c>
       <c r="B10" t="n">
         <v>57529</v>
@@ -1624,7 +1627,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1632,14 +1639,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596645</v>
+        <v>596692</v>
       </c>
       <c r="R10" t="n">
-        <v>6924182</v>
+        <v>6923986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1703,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937848</v>
+        <v>124937714</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,39 +1731,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596681</v>
+        <v>596676</v>
       </c>
       <c r="R11" t="n">
-        <v>6923921</v>
+        <v>6923916</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937714</v>
+        <v>124937848</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,34 +1843,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596676</v>
+        <v>596681</v>
       </c>
       <c r="R12" t="n">
-        <v>6923916</v>
+        <v>6923921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2049,7 +2056,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124941916</v>
+        <v>124933804</v>
       </c>
       <c r="B14" t="n">
         <v>57529</v>
@@ -2082,11 +2089,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2094,14 +2097,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596692</v>
+        <v>596645</v>
       </c>
       <c r="R14" t="n">
-        <v>6923986</v>
+        <v>6924182</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,12 +2161,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1360,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124936750</v>
+        <v>124938227</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,39 +1376,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596731</v>
+        <v>596692</v>
       </c>
       <c r="R8" t="n">
-        <v>6923972</v>
+        <v>6923986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1435,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,12 +1445,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1460,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124938227</v>
+        <v>124937714</v>
       </c>
       <c r="B9" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,34 +1488,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596692</v>
+        <v>596676</v>
       </c>
       <c r="R9" t="n">
-        <v>6923986</v>
+        <v>6923916</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,19 +1572,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124941916</v>
+        <v>124933804</v>
       </c>
       <c r="B10" t="n">
         <v>57529</v>
@@ -1627,11 +1617,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1639,14 +1625,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596692</v>
+        <v>596645</v>
       </c>
       <c r="R10" t="n">
-        <v>6923986</v>
+        <v>6924182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,19 +1689,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937714</v>
+        <v>124937225</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1751,14 +1737,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596676</v>
+        <v>596705</v>
       </c>
       <c r="R11" t="n">
-        <v>6923916</v>
+        <v>6923956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,22 +1801,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937848</v>
+        <v>124936750</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,16 +1829,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1863,7 +1849,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1872,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596681</v>
+        <v>596731</v>
       </c>
       <c r="R12" t="n">
-        <v>6923921</v>
+        <v>6923972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1903,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,22 +1923,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124937225</v>
+        <v>124937848</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,34 +1951,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596705</v>
+        <v>596681</v>
       </c>
       <c r="R13" t="n">
-        <v>6923956</v>
+        <v>6923921</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,19 +2040,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124933804</v>
+        <v>124941916</v>
       </c>
       <c r="B14" t="n">
         <v>57529</v>
@@ -2089,7 +2085,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2097,14 +2097,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596645</v>
+        <v>596692</v>
       </c>
       <c r="R14" t="n">
-        <v>6924182</v>
+        <v>6923986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,12 +2161,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124936892</v>
+        <v>124939853</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1269,14 +1269,11 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1318,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,12 +1325,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Äldre hackring av tretåig hackspett av tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124938227</v>
+        <v>124933804</v>
       </c>
       <c r="B8" t="n">
-        <v>82597</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596692</v>
+        <v>596645</v>
       </c>
       <c r="R8" t="n">
-        <v>6923986</v>
+        <v>6924182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,22 +1462,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937714</v>
+        <v>124936750</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596676</v>
+        <v>596731</v>
       </c>
       <c r="R9" t="n">
-        <v>6923916</v>
+        <v>6923972</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1564,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933804</v>
+        <v>124937714</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596645</v>
+        <v>596676</v>
       </c>
       <c r="R10" t="n">
-        <v>6924182</v>
+        <v>6923916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937225</v>
+        <v>124938227</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596705</v>
+        <v>596692</v>
       </c>
       <c r="R11" t="n">
-        <v>6923956</v>
+        <v>6923986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,22 +1808,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124936750</v>
+        <v>124937225</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,39 +1836,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596731</v>
+        <v>596705</v>
       </c>
       <c r="R12" t="n">
-        <v>6923972</v>
+        <v>6923956</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,12 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,19 +1920,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124937848</v>
+        <v>124941916</v>
       </c>
       <c r="B13" t="n">
         <v>57529</v>
@@ -1968,7 +1965,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1976,14 +1977,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596681</v>
+        <v>596692</v>
       </c>
       <c r="R13" t="n">
-        <v>6923921</v>
+        <v>6923986</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,19 +2041,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124941916</v>
+        <v>124937848</v>
       </c>
       <c r="B14" t="n">
         <v>57529</v>
@@ -2085,11 +2086,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2097,14 +2094,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596692</v>
+        <v>596681</v>
       </c>
       <c r="R14" t="n">
-        <v>6923986</v>
+        <v>6923921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,12 +2158,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1708,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124938227</v>
+        <v>124937225</v>
       </c>
       <c r="B11" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596692</v>
+        <v>596705</v>
       </c>
       <c r="R11" t="n">
-        <v>6923986</v>
+        <v>6923956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,22 +1808,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937225</v>
+        <v>124938227</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596705</v>
+        <v>596692</v>
       </c>
       <c r="R12" t="n">
-        <v>6923956</v>
+        <v>6923986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,12 +1920,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939853</v>
+        <v>124941916</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,16 +1251,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1268,10 +1268,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hackring av tretåig hackspett av tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124933804</v>
+        <v>124939853</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,16 +1372,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1393,19 +1392,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596645</v>
+        <v>596692</v>
       </c>
       <c r="R8" t="n">
-        <v>6924182</v>
+        <v>6923986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre hackring av tretåig hackspett av tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124936750</v>
+        <v>124937714</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,39 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596731</v>
+        <v>596676</v>
       </c>
       <c r="R9" t="n">
-        <v>6923972</v>
+        <v>6923916</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,12 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1578,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937714</v>
+        <v>124933804</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1606,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596676</v>
+        <v>596645</v>
       </c>
       <c r="R10" t="n">
-        <v>6923916</v>
+        <v>6924182</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937225</v>
+        <v>124938227</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,21 +1723,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596705</v>
+        <v>596692</v>
       </c>
       <c r="R11" t="n">
-        <v>6923956</v>
+        <v>6923986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,22 +1807,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124938227</v>
+        <v>124937225</v>
       </c>
       <c r="B12" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1835,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596692</v>
+        <v>596705</v>
       </c>
       <c r="R12" t="n">
-        <v>6923986</v>
+        <v>6923956</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1919,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941916</v>
+        <v>124936750</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,16 +1947,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1965,26 +1964,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596692</v>
+        <v>596731</v>
       </c>
       <c r="R13" t="n">
-        <v>6923986</v>
+        <v>6923972</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,12 +2041,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941916</v>
+        <v>124937714</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,43 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596692</v>
+        <v>596676</v>
       </c>
       <c r="R7" t="n">
-        <v>6923986</v>
+        <v>6923916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,22 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124939853</v>
+        <v>124938227</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,29 +1363,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1436,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre hackring av tretåig hackspett av tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937714</v>
+        <v>124939853</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596676</v>
+        <v>596692</v>
       </c>
       <c r="R9" t="n">
-        <v>6923916</v>
+        <v>6923986</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre hackring av tretåig hackspett av tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124933804</v>
+        <v>124937225</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,39 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596645</v>
+        <v>596705</v>
       </c>
       <c r="R10" t="n">
-        <v>6924182</v>
+        <v>6923956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124938227</v>
+        <v>124937848</v>
       </c>
       <c r="B11" t="n">
-        <v>82597</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,34 +1709,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596692</v>
+        <v>596681</v>
       </c>
       <c r="R11" t="n">
-        <v>6923986</v>
+        <v>6923921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937225</v>
+        <v>124933804</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596705</v>
+        <v>596645</v>
       </c>
       <c r="R12" t="n">
-        <v>6923956</v>
+        <v>6924182</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,22 +1915,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124936750</v>
+        <v>124941916</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,16 +1943,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1964,22 +1960,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596731</v>
+        <v>596692</v>
       </c>
       <c r="R13" t="n">
-        <v>6923972</v>
+        <v>6923986</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,22 +2036,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124937848</v>
+        <v>124936750</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,16 +2064,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2089,7 +2084,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2098,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596681</v>
+        <v>596731</v>
       </c>
       <c r="R14" t="n">
-        <v>6923921</v>
+        <v>6923972</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,12 +2158,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937714</v>
+        <v>124937848</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596676</v>
+        <v>596681</v>
       </c>
       <c r="R7" t="n">
-        <v>6923916</v>
+        <v>6923921</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124938227</v>
+        <v>124937225</v>
       </c>
       <c r="B8" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596692</v>
+        <v>596705</v>
       </c>
       <c r="R8" t="n">
-        <v>6923986</v>
+        <v>6923956</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1452,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124939853</v>
+        <v>124941916</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,16 +1480,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1492,10 +1497,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1539,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,12 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre hackring av tretåig hackspett av tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937225</v>
+        <v>124938227</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596705</v>
+        <v>596692</v>
       </c>
       <c r="R10" t="n">
-        <v>6923956</v>
+        <v>6923986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,19 +1685,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937848</v>
+        <v>124933804</v>
       </c>
       <c r="B11" t="n">
         <v>57529</v>
@@ -1738,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596681</v>
+        <v>596645</v>
       </c>
       <c r="R11" t="n">
-        <v>6923921</v>
+        <v>6924182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933804</v>
+        <v>124936892</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,16 +1830,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1844,21 +1848,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596645</v>
+        <v>596692</v>
       </c>
       <c r="R12" t="n">
-        <v>6924182</v>
+        <v>6923986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1907,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,22 +1927,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941916</v>
+        <v>124936750</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,16 +1955,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1960,26 +1972,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596692</v>
+        <v>596731</v>
       </c>
       <c r="R13" t="n">
-        <v>6923986</v>
+        <v>6923972</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2029,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,22 +2049,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124936750</v>
+        <v>124937714</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,39 +2077,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596731</v>
+        <v>596676</v>
       </c>
       <c r="R14" t="n">
-        <v>6923972</v>
+        <v>6923916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,12 +2161,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937225</v>
+        <v>124938227</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596705</v>
+        <v>596692</v>
       </c>
       <c r="R8" t="n">
-        <v>6923956</v>
+        <v>6923986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1452,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124941916</v>
+        <v>124936892</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,16 +1480,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1497,16 +1497,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1548,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124938227</v>
+        <v>124937714</v>
       </c>
       <c r="B10" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,34 +1605,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596692</v>
+        <v>596676</v>
       </c>
       <c r="R10" t="n">
-        <v>6923986</v>
+        <v>6923916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,22 +1689,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933804</v>
+        <v>124936750</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,16 +1717,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1733,7 +1737,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1742,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596645</v>
+        <v>596731</v>
       </c>
       <c r="R11" t="n">
-        <v>6924182</v>
+        <v>6923972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1791,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,22 +1811,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124936892</v>
+        <v>124933804</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,16 +1839,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1848,24 +1857,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596692</v>
+        <v>596645</v>
       </c>
       <c r="R12" t="n">
-        <v>6923986</v>
+        <v>6924182</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,12 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,22 +1928,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124936750</v>
+        <v>124941916</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,16 +1956,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,22 +1973,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596731</v>
+        <v>596692</v>
       </c>
       <c r="R13" t="n">
-        <v>6923972</v>
+        <v>6923986</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,12 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,19 +2049,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124937714</v>
+        <v>124937225</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2097,14 +2097,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596676</v>
+        <v>596705</v>
       </c>
       <c r="R14" t="n">
-        <v>6923916</v>
+        <v>6923956</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,12 +2161,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937848</v>
+        <v>124939853</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,16 +1251,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1271,19 +1271,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596681</v>
+        <v>596692</v>
       </c>
       <c r="R7" t="n">
-        <v>6923921</v>
+        <v>6923986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hackring av tretåig hackspett av tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124938227</v>
+        <v>124936750</v>
       </c>
       <c r="B8" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596692</v>
+        <v>596731</v>
       </c>
       <c r="R8" t="n">
-        <v>6923986</v>
+        <v>6923972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124936892</v>
+        <v>124938227</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,32 +1495,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1547,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,12 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937714</v>
+        <v>124937848</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596676</v>
+        <v>596681</v>
       </c>
       <c r="R10" t="n">
-        <v>6923916</v>
+        <v>6923921</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124936750</v>
+        <v>124933804</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,16 +1724,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1737,7 +1744,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1746,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596731</v>
+        <v>596645</v>
       </c>
       <c r="R11" t="n">
-        <v>6923972</v>
+        <v>6924182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,12 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,19 +1813,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124933804</v>
+        <v>124941916</v>
       </c>
       <c r="B12" t="n">
         <v>57529</v>
@@ -1856,7 +1858,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1864,14 +1870,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596645</v>
+        <v>596692</v>
       </c>
       <c r="R12" t="n">
-        <v>6924182</v>
+        <v>6923986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,22 +1934,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941916</v>
+        <v>124937225</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,43 +1962,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596692</v>
+        <v>596705</v>
       </c>
       <c r="R13" t="n">
-        <v>6923986</v>
+        <v>6923956</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,19 +2046,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124937225</v>
+        <v>124937714</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2097,14 +2094,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596705</v>
+        <v>596676</v>
       </c>
       <c r="R14" t="n">
-        <v>6923956</v>
+        <v>6923916</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,12 +2158,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124939853</v>
+        <v>124936750</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,14 +1276,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596692</v>
+        <v>596731</v>
       </c>
       <c r="R7" t="n">
-        <v>6923986</v>
+        <v>6923972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre hackring av tretåig hackspett av tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124936750</v>
+        <v>124937714</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596731</v>
+        <v>596676</v>
       </c>
       <c r="R8" t="n">
-        <v>6923972</v>
+        <v>6923916</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124938227</v>
+        <v>124936892</v>
       </c>
       <c r="B9" t="n">
-        <v>82597</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,24 +1485,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1554,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1562,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124937848</v>
+        <v>124938227</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>82737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1610,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596681</v>
+        <v>596692</v>
       </c>
       <c r="R10" t="n">
-        <v>6923921</v>
+        <v>6923986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1694,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124933804</v>
+        <v>124941916</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,7 +1739,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1749,14 +1751,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596645</v>
+        <v>596692</v>
       </c>
       <c r="R11" t="n">
-        <v>6924182</v>
+        <v>6923986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124941916</v>
+        <v>124937848</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,11 +1860,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1870,14 +1868,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596692</v>
+        <v>596681</v>
       </c>
       <c r="R12" t="n">
-        <v>6923986</v>
+        <v>6923921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,22 +1932,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124937225</v>
+        <v>124933804</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57632</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,34 +1960,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596705</v>
+        <v>596645</v>
       </c>
       <c r="R13" t="n">
-        <v>6923956</v>
+        <v>6924182</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,22 +2049,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124937714</v>
+        <v>124937225</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,14 +2097,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596676</v>
+        <v>596705</v>
       </c>
       <c r="R14" t="n">
-        <v>6923916</v>
+        <v>6923956</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,12 +2161,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124936750</v>
+        <v>124937714</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,39 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596731</v>
+        <v>596676</v>
       </c>
       <c r="R7" t="n">
-        <v>6923972</v>
+        <v>6923916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124937714</v>
+        <v>124936750</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1363,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596676</v>
+        <v>596731</v>
       </c>
       <c r="R8" t="n">
-        <v>6923916</v>
+        <v>6923972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1437,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,12 +1457,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937714</v>
+        <v>124937225</v>
       </c>
       <c r="B7" t="n">
         <v>78947</v>
@@ -1271,14 +1271,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596676</v>
+        <v>596705</v>
       </c>
       <c r="R7" t="n">
-        <v>6923916</v>
+        <v>6923956</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,22 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124936750</v>
+        <v>124941916</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1380,22 +1380,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596731</v>
+        <v>596692</v>
       </c>
       <c r="R8" t="n">
-        <v>6923972</v>
+        <v>6923986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,22 +1456,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124936892</v>
+        <v>124938227</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>82737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,32 +1484,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1552,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,12 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124938227</v>
+        <v>124936892</v>
       </c>
       <c r="B10" t="n">
-        <v>82737</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,24 +1596,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1669,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1673,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,7 +1705,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124941916</v>
+        <v>124937848</v>
       </c>
       <c r="B11" t="n">
         <v>57632</v>
@@ -1739,11 +1738,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1751,14 +1746,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596692</v>
+        <v>596681</v>
       </c>
       <c r="R11" t="n">
-        <v>6923986</v>
+        <v>6923921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937848</v>
+        <v>124937714</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,39 +1838,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596681</v>
+        <v>596676</v>
       </c>
       <c r="R12" t="n">
-        <v>6923921</v>
+        <v>6923916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124937225</v>
+        <v>124936750</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,34 +2067,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596705</v>
+        <v>596731</v>
       </c>
       <c r="R14" t="n">
-        <v>6923956</v>
+        <v>6923972</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2141,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,12 +2161,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1235,15 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937225</v>
+        <v>124937848</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,34 +1246,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596705</v>
+        <v>596681</v>
       </c>
       <c r="R7" t="n">
-        <v>6923956</v>
+        <v>6923921</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,28 +1335,23 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124941916</v>
+        <v>124933804</v>
       </c>
       <c r="B8" t="n">
         <v>57632</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1380,11 +1375,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1392,14 +1383,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596692</v>
+        <v>596645</v>
       </c>
       <c r="R8" t="n">
-        <v>6923986</v>
+        <v>6924182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,27 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124938227</v>
+        <v>124937225</v>
       </c>
       <c r="B9" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596692</v>
+        <v>596705</v>
       </c>
       <c r="R9" t="n">
-        <v>6923986</v>
+        <v>6923956</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,12 +1554,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1585,11 +1571,6 @@
       <c r="B10" t="n">
         <v>57635</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1705,15 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124937848</v>
+        <v>124936750</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,16 +1697,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1741,7 +1717,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1750,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596681</v>
+        <v>596731</v>
       </c>
       <c r="R11" t="n">
-        <v>6923921</v>
+        <v>6923972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1771,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,27 +1791,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124937714</v>
+        <v>124941916</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,34 +1814,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596676</v>
+        <v>596692</v>
       </c>
       <c r="R12" t="n">
-        <v>6923916</v>
+        <v>6923986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,27 +1907,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124933804</v>
+        <v>124937714</v>
       </c>
       <c r="B13" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,39 +1930,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596645</v>
+        <v>596676</v>
       </c>
       <c r="R13" t="n">
-        <v>6924182</v>
+        <v>6923916</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,15 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124936750</v>
+        <v>124938227</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,39 +2037,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596731</v>
+        <v>596692</v>
       </c>
       <c r="R14" t="n">
-        <v>6923972</v>
+        <v>6923986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,12 +2106,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,12 +2121,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>124937848</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>124933804</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>124941916</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>124937848</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>124933804</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>124941916</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>124937848</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>124933804</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>124941916</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>124937848</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>124933804</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>124941916</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>124937848</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>124933804</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>124941916</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>124937848</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>124933804</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>124941916</v>
       </c>
       <c r="B12" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>124936892</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>124936750</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>124936892</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>124936750</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105899205</v>
+        <v>124938227</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärdalsberget, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596634.5979008778</v>
+        <v>596692</v>
       </c>
       <c r="R2" t="n">
-        <v>6924239.451532485</v>
+        <v>6923986</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,49 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105899119</v>
+        <v>105899147</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596695.2937612321</v>
+        <v>596708</v>
       </c>
       <c r="R3" t="n">
-        <v>6924098.498093368</v>
+        <v>6923987</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +850,9 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,16 +882,11 @@
         <v>105899148</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596702.3713332835</v>
+        <v>596703</v>
       </c>
       <c r="R4" t="n">
-        <v>6924158.476536588</v>
+        <v>6924158</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +947,9 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,53 +976,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105899109</v>
+        <v>124937225</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärdalsberget, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596660.0375469342</v>
+        <v>596705</v>
       </c>
       <c r="R5" t="n">
-        <v>6923970.04906517</v>
+        <v>6923956</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1041,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,31 +1071,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105899147</v>
+        <v>124937714</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1159,17 +1114,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjärdalsberget, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596707.7882839305</v>
+        <v>596676</v>
       </c>
       <c r="R6" t="n">
-        <v>6923987.651467276</v>
+        <v>6923916</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1148,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124937848</v>
+        <v>105899119</v>
       </c>
       <c r="B7" t="n">
-        <v>57681</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,42 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596681</v>
+        <v>596696</v>
       </c>
       <c r="R7" t="n">
-        <v>6923921</v>
+        <v>6924098</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:59</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:59</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1350,11 +1290,11 @@
         <v>124933804</v>
       </c>
       <c r="B8" t="n">
-        <v>57681</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1459,45 +1399,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124937225</v>
+        <v>124937848</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596705</v>
+        <v>596681</v>
       </c>
       <c r="R9" t="n">
-        <v>6923956</v>
+        <v>6923921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1474,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1484,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,39 +1499,39 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124936892</v>
+        <v>124941916</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1594,15 +1539,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1644,7 +1590,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,12 +1600,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124936750</v>
+        <v>124936268</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596731</v>
+        <v>596604</v>
       </c>
       <c r="R11" t="n">
-        <v>6923972</v>
+        <v>6924047</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,7 +1702,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1712,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1791,22 +1732,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124941916</v>
+        <v>124936683</v>
       </c>
       <c r="B12" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,16 +1755,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1831,26 +1772,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596692</v>
+        <v>596734</v>
       </c>
       <c r="R12" t="n">
-        <v>6923986</v>
+        <v>6923966</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1819,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1829,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,22 +1849,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124937714</v>
+        <v>124936750</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,34 +1872,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596676</v>
+        <v>596731</v>
       </c>
       <c r="R13" t="n">
-        <v>6923916</v>
+        <v>6923972</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +1946,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,22 +1966,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124938227</v>
+        <v>124936892</v>
       </c>
       <c r="B14" t="n">
-        <v>82737</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,24 +1989,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -2096,7 +2056,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2106,7 +2066,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,6 +2095,200 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105899205</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjärdalsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>596634</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6924240</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105899109</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjärdalsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>596660</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6923970</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16656-2025 artfynd.xlsx
+++ b/artfynd/A 16656-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124938227</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899148</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124937225</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124937714</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899119</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124933804</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124937848</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941916</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124936268</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124936683</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1975,6 +2035,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124936750</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2095,6 +2160,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124936892</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2192,6 +2262,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899205</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2289,8 +2364,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899109</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>